--- a/data/trans_dic/P25A$preocupacion-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25A$preocupacion-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,94</t>
+          <t>0,0; 49,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,17</t>
+          <t>0,0; 38,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,88</t>
+          <t>0,0; 22,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,97</t>
+          <t>0,0; 35,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,8</t>
+          <t>0,0; 23,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 22,45</t>
+          <t>2,59; 24,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,86</t>
+          <t>0,0; 22,94</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 23,03</t>
+          <t>2,27; 21,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 14,27</t>
+          <t>2,52; 13,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 21,56</t>
+          <t>2,23; 24,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,68; 26,49</t>
+          <t>8,33; 25,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 14,76</t>
+          <t>2,61; 13,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 18,74</t>
+          <t>3,18; 18,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 20,87</t>
+          <t>7,58; 20,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 12,01</t>
+          <t>3,57; 12,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,52; 17,36</t>
+          <t>4,96; 16,37</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 21,09</t>
+          <t>5,82; 20,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 19,41</t>
+          <t>6,86; 19,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 17,39</t>
+          <t>3,91; 17,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,65</t>
+          <t>0,0; 14,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 15,46</t>
+          <t>4,54; 15,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 12,12</t>
+          <t>2,02; 11,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,67; 12,53</t>
+          <t>3,84; 13,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 15,59</t>
+          <t>6,52; 14,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 11,76</t>
+          <t>3,88; 12,1</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 15,39</t>
+          <t>4,67; 15,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 14,83</t>
+          <t>5,25; 15,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 21,59</t>
+          <t>8,33; 22,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 19,29</t>
+          <t>2,11; 19,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 20,06</t>
+          <t>5,57; 21,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 22,88</t>
+          <t>7,61; 22,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 13,93</t>
+          <t>4,72; 13,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 14,8</t>
+          <t>6,91; 14,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 20,12</t>
+          <t>10,05; 20,12</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 9,69</t>
+          <t>2,27; 10,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 15,81</t>
+          <t>4,43; 15,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,04; 18,73</t>
+          <t>6,85; 18,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,29</t>
+          <t>0,0; 28,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,84</t>
+          <t>1,76; 15,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,05</t>
+          <t>0,0; 17,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 9,99</t>
+          <t>2,53; 11,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 13,06</t>
+          <t>4,35; 12,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 15,32</t>
+          <t>5,14; 14,84</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 10,38</t>
+          <t>2,27; 10,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,67</t>
+          <t>1,29; 7,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,9; 25,32</t>
+          <t>10,8; 25,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,75</t>
+          <t>0,0; 27,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,32</t>
+          <t>0,0; 21,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,69; 9,91</t>
+          <t>2,61; 10,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,42</t>
+          <t>1,66; 7,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,0; 21,44</t>
+          <t>9,43; 21,09</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,71; 12,85</t>
+          <t>3,83; 13,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 12,44</t>
+          <t>2,7; 11,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 15,52</t>
+          <t>4,75; 15,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,62</t>
+          <t>0,0; 56,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,01; 13,83</t>
+          <t>3,79; 13,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 11,48</t>
+          <t>2,57; 11,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,27; 14,46</t>
+          <t>4,54; 15,15</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,94</t>
+          <t>5,66; 10,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,0; 9,94</t>
+          <t>5,93; 9,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,35; 14,89</t>
+          <t>9,63; 14,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,27; 12,65</t>
+          <t>4,89; 12,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,53; 11,3</t>
+          <t>5,37; 11,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,52; 11,36</t>
+          <t>5,47; 11,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,87</t>
+          <t>6,03; 9,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,77</t>
+          <t>6,35; 9,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,84; 12,86</t>
+          <t>8,78; 12,93</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5411</t>
+          <t>0; 5549</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6910</t>
+          <t>0; 6469</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1770</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1827</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4784</t>
+          <t>0; 4285</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5934</t>
+          <t>0; 5865</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6362</t>
+          <t>0; 6365</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>951; 8085</t>
+          <t>933; 8756</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5932</t>
+          <t>0; 5952</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>913; 9085</t>
+          <t>896; 8625</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1247; 10382</t>
+          <t>1834; 10095</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1083; 10478</t>
+          <t>1085; 11820</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6079; 18558</t>
+          <t>5834; 17795</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2101; 12234</t>
+          <t>2161; 11403</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1860; 10866</t>
+          <t>1842; 10936</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8084; 22852</t>
+          <t>8302; 22298</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5789; 18694</t>
+          <t>5557; 18753</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4822; 18500</t>
+          <t>5282; 17440</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4892; 17916</t>
+          <t>4943; 17712</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7111; 21807</t>
+          <t>7712; 21899</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2964; 12928</t>
+          <t>2906; 12997</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 7720</t>
+          <t>0; 9624</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4969; 19189</t>
+          <t>5634; 19653</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1819; 10657</t>
+          <t>1773; 10282</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5545; 18940</t>
+          <t>5802; 20780</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16315; 36862</t>
+          <t>15422; 34808</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5760; 19084</t>
+          <t>6291; 19625</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5872; 19321</t>
+          <t>5858; 19532</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9647; 25208</t>
+          <t>8915; 25600</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8351; 23359</t>
+          <t>9012; 24805</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1243; 11331</t>
+          <t>1241; 11717</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4523; 18371</t>
+          <t>5098; 19538</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6372; 20187</t>
+          <t>6716; 20172</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8904; 25664</t>
+          <t>8690; 25528</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18050; 38707</t>
+          <t>18079; 38344</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18917; 39511</t>
+          <t>19731; 39519</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2862; 12415</t>
+          <t>2906; 13437</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6331; 22176</t>
+          <t>6214; 21587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9356; 24908</t>
+          <t>9104; 24847</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 6154</t>
+          <t>0; 4978</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 7165</t>
+          <t>911; 8184</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 8565</t>
+          <t>0; 9685</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3758; 14547</t>
+          <t>3688; 16263</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8531; 25074</t>
+          <t>8351; 24670</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10408; 29103</t>
+          <t>9754; 28179</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2832; 12654</t>
+          <t>2771; 12713</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2159; 12472</t>
+          <t>2101; 12139</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13429; 31199</t>
+          <t>13305; 31697</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4571</t>
+          <t>0; 3753</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1814</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4461</t>
+          <t>0; 5581</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3645; 13421</t>
+          <t>3537; 13563</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2091; 12843</t>
+          <t>2868; 12571</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13409; 31939</t>
+          <t>14055; 31425</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4201; 14554</t>
+          <t>4334; 15236</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3917; 17605</t>
+          <t>3826; 15777</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4875; 16878</t>
+          <t>5159; 16880</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 5320</t>
+          <t>0; 5216</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1693</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 1420</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4909; 16947</t>
+          <t>4647; 16781</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3249; 16976</t>
+          <t>3802; 17636</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4749; 16079</t>
+          <t>5044; 16848</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>36167; 62083</t>
+          <t>35340; 63240</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>48967; 81135</t>
+          <t>48425; 80815</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>56644; 90187</t>
+          <t>58291; 90426</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13204; 31723</t>
+          <t>12250; 30475</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>21379; 43687</t>
+          <t>20743; 43260</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18524; 38153</t>
+          <t>18371; 38529</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>53133; 86402</t>
+          <t>52820; 86850</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>76504; 117461</t>
+          <t>76378; 117202</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>83249; 121094</t>
+          <t>82691; 121724</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$preocupacion-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25A$preocupacion-Edad-trans_dic.xlsx
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,15</t>
+          <t>0,0; 48,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,54</t>
+          <t>0,0; 37,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,28</t>
+          <t>0,0; 27,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,55</t>
+          <t>0,0; 35,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,81</t>
+          <t>0,0; 23,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 24,31</t>
+          <t>2,58; 23,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,94</t>
+          <t>0,0; 22,81</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 21,86</t>
+          <t>2,16; 22,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 13,88</t>
+          <t>2,49; 14,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 24,32</t>
+          <t>2,25; 22,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,33; 25,4</t>
+          <t>8,64; 26,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 13,76</t>
+          <t>3,35; 15,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 18,87</t>
+          <t>4,16; 19,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,58; 20,36</t>
+          <t>7,47; 20,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 12,05</t>
+          <t>3,72; 12,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 16,37</t>
+          <t>4,98; 16,27</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 20,85</t>
+          <t>5,63; 20,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 19,49</t>
+          <t>7,2; 19,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 17,49</t>
+          <t>3,85; 17,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,52</t>
+          <t>0,0; 11,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 15,84</t>
+          <t>4,06; 15,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 11,69</t>
+          <t>2,06; 11,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 13,74</t>
+          <t>3,91; 13,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 14,72</t>
+          <t>6,41; 14,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 12,1</t>
+          <t>3,96; 12,11</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 15,56</t>
+          <t>4,11; 15,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 15,06</t>
+          <t>5,69; 14,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,33; 22,93</t>
+          <t>8,24; 22,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 19,94</t>
+          <t>2,14; 18,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 21,33</t>
+          <t>5,85; 20,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,61; 22,86</t>
+          <t>7,24; 22,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 13,85</t>
+          <t>4,87; 13,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 14,66</t>
+          <t>6,78; 14,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 20,12</t>
+          <t>9,76; 20,15</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,49</t>
+          <t>2,25; 9,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 15,39</t>
+          <t>4,65; 15,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,85; 18,68</t>
+          <t>6,78; 19,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,54</t>
+          <t>0,0; 34,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 15,81</t>
+          <t>1,73; 15,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,02</t>
+          <t>0,0; 13,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 11,17</t>
+          <t>2,52; 10,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,35; 12,85</t>
+          <t>4,35; 13,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 14,84</t>
+          <t>5,43; 15,38</t>
         </is>
       </c>
     </row>
@@ -1228,22 +1228,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,43</t>
+          <t>2,3; 10,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,47</t>
+          <t>1,3; 7,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,8; 25,72</t>
+          <t>10,33; 24,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,71</t>
+          <t>0,0; 33,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1253,22 +1253,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,66</t>
+          <t>0,0; 21,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,61; 10,01</t>
+          <t>2,68; 10,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 7,26</t>
+          <t>1,23; 7,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,43; 21,09</t>
+          <t>9,07; 20,96</t>
         </is>
       </c>
     </row>
@@ -1338,22 +1338,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,83; 13,45</t>
+          <t>3,48; 13,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,7; 11,15</t>
+          <t>2,62; 12,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,75; 15,53</t>
+          <t>4,66; 14,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,49</t>
+          <t>0,0; 56,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 13,69</t>
+          <t>3,78; 13,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 11,93</t>
+          <t>2,62; 11,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 15,15</t>
+          <t>4,5; 14,29</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,66; 10,13</t>
+          <t>5,79; 10,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,93; 9,9</t>
+          <t>5,88; 9,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,63; 14,93</t>
+          <t>9,32; 14,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,89; 12,15</t>
+          <t>5,27; 12,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,37; 11,19</t>
+          <t>5,51; 11,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,47; 11,47</t>
+          <t>5,61; 11,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,92</t>
+          <t>6,11; 9,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,35; 9,75</t>
+          <t>6,39; 9,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,78; 12,93</t>
+          <t>8,66; 12,71</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5549</t>
+          <t>0; 5492</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6469</t>
+          <t>0; 6324</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1770,27 +1770,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4285</t>
+          <t>0; 5200</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5865</t>
+          <t>0; 5898</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6365</t>
+          <t>0; 6347</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>933; 8756</t>
+          <t>928; 8568</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5952</t>
+          <t>0; 5918</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>896; 8625</t>
+          <t>853; 8949</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1834; 10095</t>
+          <t>1808; 10208</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1085; 11820</t>
+          <t>1093; 11039</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5834; 17795</t>
+          <t>6050; 18438</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2161; 11403</t>
+          <t>2777; 13178</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1842; 10936</t>
+          <t>2412; 11065</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8302; 22298</t>
+          <t>8176; 22827</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5557; 18753</t>
+          <t>5786; 18963</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5282; 17440</t>
+          <t>5307; 17341</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4943; 17712</t>
+          <t>4785; 17275</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7712; 21899</t>
+          <t>8088; 22247</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2906; 12997</t>
+          <t>2861; 12911</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 9624</t>
+          <t>0; 7336</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5634; 19653</t>
+          <t>5035; 18686</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1773; 10282</t>
+          <t>1810; 10279</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5802; 20780</t>
+          <t>5912; 20232</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15422; 34808</t>
+          <t>15169; 35174</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6291; 19625</t>
+          <t>6427; 19642</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5858; 19532</t>
+          <t>5163; 19721</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8915; 25600</t>
+          <t>9668; 24660</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9012; 24805</t>
+          <t>8912; 24075</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1241; 11717</t>
+          <t>1257; 11096</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5098; 19538</t>
+          <t>5357; 18341</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6716; 20172</t>
+          <t>6387; 19769</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8690; 25528</t>
+          <t>8976; 24911</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18079; 38344</t>
+          <t>17734; 37993</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19731; 39519</t>
+          <t>19177; 39579</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2906; 13437</t>
+          <t>2884; 12657</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6214; 21587</t>
+          <t>6523; 21088</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9104; 24847</t>
+          <t>9020; 25818</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4978</t>
+          <t>0; 6078</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>911; 8184</t>
+          <t>895; 7914</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 9685</t>
+          <t>0; 7762</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3688; 16263</t>
+          <t>3664; 14967</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8351; 24670</t>
+          <t>8343; 25994</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9754; 28179</t>
+          <t>10316; 29213</t>
         </is>
       </c>
     </row>
@@ -2565,22 +2565,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2771; 12713</t>
+          <t>2803; 12720</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2101; 12139</t>
+          <t>2121; 11827</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13305; 31697</t>
+          <t>12733; 30679</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3753</t>
+          <t>0; 4550</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2590,22 +2590,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5581</t>
+          <t>0; 5415</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3537; 13563</t>
+          <t>3631; 14420</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2868; 12571</t>
+          <t>2133; 12934</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14055; 31425</t>
+          <t>13509; 31225</t>
         </is>
       </c>
     </row>
@@ -2728,22 +2728,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4334; 15236</t>
+          <t>3948; 14727</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3826; 15777</t>
+          <t>3702; 17418</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5159; 16880</t>
+          <t>5072; 15804</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 5216</t>
+          <t>0; 5179</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2758,17 +2758,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4647; 16781</t>
+          <t>4637; 16022</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3802; 17636</t>
+          <t>3880; 17006</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5044; 16848</t>
+          <t>5002; 15896</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>35340; 63240</t>
+          <t>36141; 63195</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>48425; 80815</t>
+          <t>48021; 80630</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>58291; 90426</t>
+          <t>56420; 89752</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12250; 30475</t>
+          <t>13218; 31847</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>20743; 43260</t>
+          <t>21302; 45371</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18371; 38529</t>
+          <t>18835; 39684</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>52820; 86850</t>
+          <t>53517; 85331</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>76378; 117202</t>
+          <t>76889; 116045</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>82691; 121724</t>
+          <t>81514; 119615</t>
         </is>
       </c>
     </row>
